--- a/public/demos/re-developer/dev-pro-forma.xlsx
+++ b/public/demos/re-developer/dev-pro-forma.xlsx
@@ -685,7 +685,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>The Reserve at Oak Park</t>
+          <t>The Reserve at Royal Oak</t>
         </is>
       </c>
     </row>
@@ -699,7 +699,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>4800 Coolidge Hwy, Oak Park, MI 48237</t>
+          <t>1200 N Main St, Royal Oak, MI 48067</t>
         </is>
       </c>
     </row>
@@ -760,7 +760,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>8.5</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="11">
@@ -916,7 +916,7 @@
         </is>
       </c>
       <c r="B27" s="10">
-        <f>'Waterfall'!B16</f>
+        <f>'Waterfall'!B17</f>
         <v/>
       </c>
     </row>
@@ -927,7 +927,7 @@
         </is>
       </c>
       <c r="B28" s="11">
-        <f>'Waterfall'!B13</f>
+        <f>'Waterfall'!B14</f>
         <v/>
       </c>
     </row>
@@ -938,7 +938,7 @@
         </is>
       </c>
       <c r="B29" s="11">
-        <f>'Waterfall'!B14</f>
+        <f>'Waterfall'!B15</f>
         <v/>
       </c>
     </row>
@@ -949,7 +949,7 @@
         </is>
       </c>
       <c r="B30" s="12">
-        <f>'Waterfall'!B15</f>
+        <f>'Waterfall'!B16</f>
         <v/>
       </c>
     </row>
@@ -1059,7 +1059,7 @@
       </c>
       <c r="B3" s="15" t="inlineStr">
         <is>
-          <t>The Reserve at Oak Park</t>
+          <t>The Reserve at Royal Oak</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr"/>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="B4" s="15" t="inlineStr">
         <is>
-          <t>4800 Coolidge Hwy, Oak Park, MI 48237</t>
+          <t>1200 N Main St, Royal Oak, MI 48067</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr"/>
@@ -1148,7 +1148,7 @@
         </is>
       </c>
       <c r="B9" s="18" t="n">
-        <v>8.5</v>
+        <v>4.2</v>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
@@ -1339,7 +1339,7 @@
         </is>
       </c>
       <c r="B26" s="19" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         </is>
       </c>
       <c r="B27" s="20" t="n">
-        <v>1900</v>
+        <v>1100</v>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
@@ -1371,7 +1371,7 @@
         </is>
       </c>
       <c r="B28" s="20" t="n">
-        <v>950</v>
+        <v>600</v>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
         </is>
       </c>
       <c r="B29" s="20" t="n">
-        <v>500</v>
+        <v>350</v>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
@@ -1403,7 +1403,7 @@
         </is>
       </c>
       <c r="B30" s="20" t="n">
-        <v>375</v>
+        <v>250</v>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
@@ -1419,7 +1419,7 @@
         </is>
       </c>
       <c r="B31" s="20" t="n">
-        <v>625</v>
+        <v>425</v>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
@@ -1435,7 +1435,7 @@
         </is>
       </c>
       <c r="B32" s="20" t="n">
-        <v>375</v>
+        <v>240</v>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
@@ -1451,7 +1451,7 @@
         </is>
       </c>
       <c r="B33" s="20" t="n">
-        <v>275</v>
+        <v>175</v>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         </is>
       </c>
       <c r="B34" s="20" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
@@ -1483,7 +1483,7 @@
         </is>
       </c>
       <c r="B35" s="20" t="n">
-        <v>850</v>
+        <v>525</v>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         </is>
       </c>
       <c r="B36" s="20" t="n">
-        <v>3200</v>
+        <v>2200</v>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
@@ -1515,7 +1515,7 @@
         </is>
       </c>
       <c r="B37" s="20" t="n">
-        <v>375</v>
+        <v>240</v>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         </is>
       </c>
       <c r="B38" s="20" t="n">
-        <v>225</v>
+        <v>150</v>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
@@ -1547,7 +1547,7 @@
         </is>
       </c>
       <c r="B39" s="20" t="n">
-        <v>350</v>
+        <v>250</v>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
@@ -1575,7 +1575,7 @@
         </is>
       </c>
       <c r="B41" s="19" t="n">
-        <v>0.1</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="C41" s="3" t="inlineStr"/>
       <c r="D41" s="3" t="inlineStr"/>
@@ -1587,7 +1587,7 @@
         </is>
       </c>
       <c r="B42" s="19" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="C42" s="3" t="inlineStr"/>
       <c r="D42" s="3" t="inlineStr"/>
@@ -1837,7 +1837,7 @@
         </is>
       </c>
       <c r="B4" s="18" t="n">
-        <v>6500000</v>
+        <v>5800000</v>
       </c>
       <c r="C4" s="22">
         <f>B4/200</f>
@@ -1871,7 +1871,7 @@
         </is>
       </c>
       <c r="B7" s="18" t="n">
-        <v>40835294.11764706</v>
+        <v>36647058.82352941</v>
       </c>
       <c r="C7" s="22">
         <f>B7/200</f>
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="B8" s="18" t="n">
-        <v>3200000</v>
+        <v>2800000</v>
       </c>
       <c r="C8" s="22">
         <f>B8/200</f>
@@ -2373,7 +2373,7 @@
         </is>
       </c>
       <c r="B37" s="9">
-        <f>B30*0.65</f>
+        <f>(0.65*(B4+B10+B21+B28))/(1-0.65*(0.01+0.0725*0.5*20/12))</f>
         <v/>
       </c>
       <c r="C37" s="23">
@@ -2530,7 +2530,7 @@
         <v>550</v>
       </c>
       <c r="D4" s="34" t="n">
-        <v>2.05</v>
+        <v>3.1</v>
       </c>
       <c r="E4" s="22">
         <f>C4*D4</f>
@@ -2554,7 +2554,7 @@
         <v>725</v>
       </c>
       <c r="D5" s="34" t="n">
-        <v>1.95</v>
+        <v>2.95</v>
       </c>
       <c r="E5" s="22">
         <f>C5*D5</f>
@@ -2578,7 +2578,7 @@
         <v>1050</v>
       </c>
       <c r="D6" s="34" t="n">
-        <v>1.8</v>
+        <v>2.75</v>
       </c>
       <c r="E6" s="22">
         <f>C6*D6</f>
@@ -2602,7 +2602,7 @@
         <v>1300</v>
       </c>
       <c r="D7" s="34" t="n">
-        <v>1.7</v>
+        <v>2.55</v>
       </c>
       <c r="E7" s="22">
         <f>C7*D7</f>
@@ -2762,9 +2762,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="35">
-        <f> Net Rental Income</f>
-        <v/>
+      <c r="A15" s="35" t="inlineStr">
+        <is>
+          <t>Net Rental Income</t>
+        </is>
       </c>
       <c r="B15" s="36">
         <f>B10+B11+B12+B13+B14</f>
@@ -2911,27 +2912,27 @@
       </c>
       <c r="B2" s="15" t="inlineStr">
         <is>
-          <t>4.0% EGI</t>
+          <t>3.0% EGI</t>
         </is>
       </c>
       <c r="C2" s="9">
-        <f>'Revenue'!B18*0.04</f>
+        <f>'Revenue'!B18*0.03</f>
         <v/>
       </c>
       <c r="D2" s="9">
-        <f>'Revenue'!C18*0.04</f>
+        <f>'Revenue'!C18*0.03</f>
         <v/>
       </c>
       <c r="E2" s="9">
-        <f>'Revenue'!D18*0.04</f>
+        <f>'Revenue'!D18*0.03</f>
         <v/>
       </c>
       <c r="F2" s="9">
-        <f>'Revenue'!E18*0.04</f>
+        <f>'Revenue'!E18*0.03</f>
         <v/>
       </c>
       <c r="G2" s="9">
-        <f>'Revenue'!F18*0.04</f>
+        <f>'Revenue'!F18*0.03</f>
         <v/>
       </c>
     </row>
@@ -2942,10 +2943,10 @@
         </is>
       </c>
       <c r="B3" s="20" t="n">
-        <v>1900</v>
+        <v>1100</v>
       </c>
       <c r="C3" s="18" t="n">
-        <v>380000</v>
+        <v>220000</v>
       </c>
       <c r="D3" s="9">
         <f>C3*(1+0.03)</f>
@@ -2971,10 +2972,10 @@
         </is>
       </c>
       <c r="B4" s="20" t="n">
-        <v>950</v>
+        <v>600</v>
       </c>
       <c r="C4" s="18" t="n">
-        <v>190000</v>
+        <v>120000</v>
       </c>
       <c r="D4" s="9">
         <f>C4*(1+0.03)</f>
@@ -3000,10 +3001,10 @@
         </is>
       </c>
       <c r="B5" s="20" t="n">
-        <v>500</v>
+        <v>350</v>
       </c>
       <c r="C5" s="18" t="n">
-        <v>100000</v>
+        <v>70000</v>
       </c>
       <c r="D5" s="9">
         <f>C5*(1+0.03)</f>
@@ -3029,10 +3030,10 @@
         </is>
       </c>
       <c r="B6" s="20" t="n">
-        <v>375</v>
+        <v>250</v>
       </c>
       <c r="C6" s="18" t="n">
-        <v>75000</v>
+        <v>50000</v>
       </c>
       <c r="D6" s="9">
         <f>C6*(1+0.03)</f>
@@ -3058,10 +3059,10 @@
         </is>
       </c>
       <c r="B7" s="20" t="n">
-        <v>625</v>
+        <v>425</v>
       </c>
       <c r="C7" s="18" t="n">
-        <v>125000</v>
+        <v>85000</v>
       </c>
       <c r="D7" s="9">
         <f>C7*(1+0.03)</f>
@@ -3087,10 +3088,10 @@
         </is>
       </c>
       <c r="B8" s="20" t="n">
-        <v>375</v>
+        <v>240</v>
       </c>
       <c r="C8" s="18" t="n">
-        <v>75000</v>
+        <v>48000</v>
       </c>
       <c r="D8" s="9">
         <f>C8*(1+0.03)</f>
@@ -3116,10 +3117,10 @@
         </is>
       </c>
       <c r="B9" s="20" t="n">
-        <v>275</v>
+        <v>175</v>
       </c>
       <c r="C9" s="18" t="n">
-        <v>55000</v>
+        <v>35000</v>
       </c>
       <c r="D9" s="9">
         <f>C9*(1+0.03)</f>
@@ -3145,10 +3146,10 @@
         </is>
       </c>
       <c r="B10" s="20" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="C10" s="18" t="n">
-        <v>60000</v>
+        <v>40000</v>
       </c>
       <c r="D10" s="9">
         <f>C10*(1+0.03)</f>
@@ -3174,25 +3175,25 @@
         </is>
       </c>
       <c r="B11" s="20" t="n">
-        <v>850</v>
+        <v>525</v>
       </c>
       <c r="C11" s="18" t="n">
-        <v>170000</v>
+        <v>105000</v>
       </c>
       <c r="D11" s="9">
-        <f>C11*(1+0.1)</f>
+        <f>C11*(1+0.07)</f>
         <v/>
       </c>
       <c r="E11" s="9">
-        <f>D11*(1+0.1)</f>
+        <f>D11*(1+0.07)</f>
         <v/>
       </c>
       <c r="F11" s="9">
-        <f>E11*(1+0.1)</f>
+        <f>E11*(1+0.07)</f>
         <v/>
       </c>
       <c r="G11" s="9">
-        <f>F11*(1+0.1)</f>
+        <f>F11*(1+0.07)</f>
         <v/>
       </c>
     </row>
@@ -3203,25 +3204,25 @@
         </is>
       </c>
       <c r="B12" s="20" t="n">
-        <v>3200</v>
+        <v>2200</v>
       </c>
       <c r="C12" s="18" t="n">
-        <v>640000</v>
+        <v>440000</v>
       </c>
       <c r="D12" s="9">
-        <f>C12*(1+0.04)</f>
+        <f>C12*(1+0.03)</f>
         <v/>
       </c>
       <c r="E12" s="9">
-        <f>D12*(1+0.04)</f>
+        <f>D12*(1+0.03)</f>
         <v/>
       </c>
       <c r="F12" s="9">
-        <f>E12*(1+0.04)</f>
+        <f>E12*(1+0.03)</f>
         <v/>
       </c>
       <c r="G12" s="9">
-        <f>F12*(1+0.04)</f>
+        <f>F12*(1+0.03)</f>
         <v/>
       </c>
     </row>
@@ -3232,10 +3233,10 @@
         </is>
       </c>
       <c r="B13" s="20" t="n">
-        <v>375</v>
+        <v>240</v>
       </c>
       <c r="C13" s="18" t="n">
-        <v>75000</v>
+        <v>48000</v>
       </c>
       <c r="D13" s="9">
         <f>C13*(1+0.03)</f>
@@ -3261,10 +3262,10 @@
         </is>
       </c>
       <c r="B14" s="20" t="n">
-        <v>225</v>
+        <v>150</v>
       </c>
       <c r="C14" s="18" t="n">
-        <v>45000</v>
+        <v>30000</v>
       </c>
       <c r="D14" s="9">
         <f>C14*(1+0.03)</f>
@@ -3290,10 +3291,10 @@
         </is>
       </c>
       <c r="B15" s="20" t="n">
-        <v>350</v>
+        <v>250</v>
       </c>
       <c r="C15" s="18" t="n">
-        <v>70000</v>
+        <v>50000</v>
       </c>
       <c r="D15" s="9">
         <f>C15*(1+0.03)</f>
@@ -3541,23 +3542,23 @@
         </is>
       </c>
       <c r="B7" s="9">
-        <f>-PMT(0.055/12,30*12,'Sources &amp; Uses'!B37*'Sources &amp; Uses'!B30*0.65/'Sources &amp; Uses'!B30)*12</f>
+        <f>PMT(0.055/12,30*12,'Sources &amp; Uses'!B30*0.65)*12</f>
         <v/>
       </c>
       <c r="C7" s="9">
-        <f>-PMT(0.055/12,30*12,'Sources &amp; Uses'!B37*'Sources &amp; Uses'!B30*0.65/'Sources &amp; Uses'!B30)*12</f>
+        <f>PMT(0.055/12,30*12,'Sources &amp; Uses'!B30*0.65)*12</f>
         <v/>
       </c>
       <c r="D7" s="9">
-        <f>-PMT(0.055/12,30*12,'Sources &amp; Uses'!B37*'Sources &amp; Uses'!B30*0.65/'Sources &amp; Uses'!B30)*12</f>
+        <f>PMT(0.055/12,30*12,'Sources &amp; Uses'!B30*0.65)*12</f>
         <v/>
       </c>
       <c r="E7" s="9">
-        <f>-PMT(0.055/12,30*12,'Sources &amp; Uses'!B37*'Sources &amp; Uses'!B30*0.65/'Sources &amp; Uses'!B30)*12</f>
+        <f>PMT(0.055/12,30*12,'Sources &amp; Uses'!B30*0.65)*12</f>
         <v/>
       </c>
       <c r="F7" s="9">
-        <f>-PMT(0.055/12,30*12,'Sources &amp; Uses'!B37*'Sources &amp; Uses'!B30*0.65/'Sources &amp; Uses'!B30)*12</f>
+        <f>PMT(0.055/12,30*12,'Sources &amp; Uses'!B30*0.65)*12</f>
         <v/>
       </c>
     </row>
@@ -3770,7 +3771,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:H17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -3921,7 +3922,10 @@
       <c r="E5" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="F5" s="9">
+      <c r="F5" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="9">
         <f>'NOI &amp; Cash Flow'!B19</f>
         <v/>
       </c>
@@ -3931,118 +3935,113 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="27" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>(-) Loan Payoff</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="9">
+        <f>FV(0.055/12,5*12,PMT(0.055/12,30*12,('Sources &amp; Uses'!B30*0.65)),('Sources &amp; Uses'!B30*0.65))</f>
+        <v/>
+      </c>
+      <c r="H6" s="9">
+        <f>SUM(B6:G6)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="27" t="inlineStr">
         <is>
           <t>Total Cash Available</t>
         </is>
       </c>
-      <c r="B6" s="28">
-        <f>B3+B4+B5</f>
-        <v/>
-      </c>
-      <c r="C6" s="28">
-        <f>C3+C4+C5</f>
-        <v/>
-      </c>
-      <c r="D6" s="28">
-        <f>D3+D4+D5</f>
-        <v/>
-      </c>
-      <c r="E6" s="28">
-        <f>E3+E4+E5</f>
-        <v/>
-      </c>
-      <c r="F6" s="28">
-        <f>F3+F4+F5</f>
-        <v/>
-      </c>
-      <c r="G6" s="28">
-        <f>G3+G4+G5</f>
-        <v/>
-      </c>
-      <c r="H6" s="28">
-        <f>H3+H4+H5</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" ht="6" customHeight="1"/>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="B7" s="28">
+        <f>B3+B4+B5+B6</f>
+        <v/>
+      </c>
+      <c r="C7" s="28">
+        <f>C3+C4+C5+C6</f>
+        <v/>
+      </c>
+      <c r="D7" s="28">
+        <f>D3+D4+D5+D6</f>
+        <v/>
+      </c>
+      <c r="E7" s="28">
+        <f>E3+E4+E5+E6</f>
+        <v/>
+      </c>
+      <c r="F7" s="28">
+        <f>F3+F4+F5+F6</f>
+        <v/>
+      </c>
+      <c r="G7" s="28">
+        <f>G3+G4+G5+G6</f>
+        <v/>
+      </c>
+      <c r="H7" s="28">
+        <f>H3+H4+H5+H6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="6" customHeight="1"/>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>LP DISTRIBUTIONS (90% equity, 8% pref)</t>
         </is>
       </c>
-      <c r="B8" s="5" t="n"/>
-      <c r="C8" s="5" t="n"/>
-      <c r="D8" s="5" t="n"/>
-      <c r="E8" s="5" t="n"/>
-      <c r="F8" s="5" t="n"/>
-      <c r="G8" s="5" t="n"/>
-      <c r="H8" s="5" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="6" t="inlineStr">
-        <is>
-          <t>LP Distributions (pro-rata)</t>
-        </is>
-      </c>
-      <c r="B9" s="9">
-        <f>IF(B6&lt;0,B6*0.9,MAX(0,B6)*0.9)</f>
-        <v/>
-      </c>
-      <c r="C9" s="9">
-        <f>IF(C6&lt;0,C6*0.9,MAX(0,C6)*0.9)</f>
-        <v/>
-      </c>
-      <c r="D9" s="9">
-        <f>IF(D6&lt;0,D6*0.9,MAX(0,D6)*0.9)</f>
-        <v/>
-      </c>
-      <c r="E9" s="9">
-        <f>IF(E6&lt;0,E6*0.9,MAX(0,E6)*0.9)</f>
-        <v/>
-      </c>
-      <c r="F9" s="9">
-        <f>IF(F6&lt;0,F6*0.9,MAX(0,F6)*0.9)</f>
-        <v/>
-      </c>
-      <c r="G9" s="9">
-        <f>IF(G6&lt;0,G6*0.9,MAX(0,G6)*0.9)</f>
-        <v/>
-      </c>
-      <c r="H9" s="9">
-        <f>SUM(B9:G9)</f>
-        <v/>
-      </c>
+      <c r="B9" s="5" t="n"/>
+      <c r="C9" s="5" t="n"/>
+      <c r="D9" s="5" t="n"/>
+      <c r="E9" s="5" t="n"/>
+      <c r="F9" s="5" t="n"/>
+      <c r="G9" s="5" t="n"/>
+      <c r="H9" s="5" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>GP Distributions (pro-rata)</t>
+          <t>LP Distributions (pro-rata)</t>
         </is>
       </c>
       <c r="B10" s="9">
-        <f>B6-B9</f>
+        <f>IF(B7&lt;0,B7*0.9,MAX(0,B7)*0.9)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>C6-C9</f>
+        <f>IF(C7&lt;0,C7*0.9,MAX(0,C7)*0.9)</f>
         <v/>
       </c>
       <c r="D10" s="9">
-        <f>D6-D9</f>
+        <f>IF(D7&lt;0,D7*0.9,MAX(0,D7)*0.9)</f>
         <v/>
       </c>
       <c r="E10" s="9">
-        <f>E6-E9</f>
+        <f>IF(E7&lt;0,E7*0.9,MAX(0,E7)*0.9)</f>
         <v/>
       </c>
       <c r="F10" s="9">
-        <f>F6-F9</f>
+        <f>IF(F7&lt;0,F7*0.9,MAX(0,F7)*0.9)</f>
         <v/>
       </c>
       <c r="G10" s="9">
-        <f>G6-G9</f>
+        <f>IF(G7&lt;0,G7*0.9,MAX(0,G7)*0.9)</f>
         <v/>
       </c>
       <c r="H10" s="9">
@@ -4050,61 +4049,96 @@
         <v/>
       </c>
     </row>
-    <row r="11" ht="6" customHeight="1"/>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>GP Distributions (pro-rata)</t>
+        </is>
+      </c>
+      <c r="B11" s="9">
+        <f>B7-B10</f>
+        <v/>
+      </c>
+      <c r="C11" s="9">
+        <f>C7-C10</f>
+        <v/>
+      </c>
+      <c r="D11" s="9">
+        <f>D7-D10</f>
+        <v/>
+      </c>
+      <c r="E11" s="9">
+        <f>E7-E10</f>
+        <v/>
+      </c>
+      <c r="F11" s="9">
+        <f>F7-F10</f>
+        <v/>
+      </c>
+      <c r="G11" s="9">
+        <f>G7-G10</f>
+        <v/>
+      </c>
+      <c r="H11" s="9">
+        <f>SUM(B11:G11)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="6" customHeight="1"/>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>RETURN METRICS</t>
         </is>
       </c>
-      <c r="B12" s="5" t="n"/>
-      <c r="C12" s="5" t="n"/>
-      <c r="D12" s="5" t="n"/>
-      <c r="E12" s="5" t="n"/>
-      <c r="F12" s="5" t="n"/>
-      <c r="G12" s="5" t="n"/>
-      <c r="H12" s="5" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="31" t="inlineStr">
-        <is>
-          <t>Unlevered IRR (Project)</t>
-        </is>
-      </c>
-      <c r="B13" s="11">
-        <f>IFERROR(IRR(B6:G6),"N/A")</f>
-        <v/>
-      </c>
+      <c r="B13" s="5" t="n"/>
+      <c r="C13" s="5" t="n"/>
+      <c r="D13" s="5" t="n"/>
+      <c r="E13" s="5" t="n"/>
+      <c r="F13" s="5" t="n"/>
+      <c r="G13" s="5" t="n"/>
+      <c r="H13" s="5" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="31" t="inlineStr">
         <is>
-          <t>LP IRR</t>
+          <t>Unlevered IRR (Project)</t>
         </is>
       </c>
       <c r="B14" s="11">
-        <f>IFERROR(IRR(B9:G9),"N/A")</f>
+        <f>IFERROR(IRR(B7:G7),"N/A")</f>
         <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="31" t="inlineStr">
         <is>
-          <t>LP Equity Multiple</t>
-        </is>
-      </c>
-      <c r="B15" s="12">
-        <f>IF('Sources &amp; Uses'!B36=0,0,(SUMPRODUCT(MAX(B9:G9,0))/'Sources &amp; Uses'!B36))</f>
+          <t>LP IRR</t>
+        </is>
+      </c>
+      <c r="B15" s="11">
+        <f>IFERROR(IRR(B10:G10),"N/A")</f>
         <v/>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="31" t="inlineStr">
         <is>
+          <t>LP Equity Multiple</t>
+        </is>
+      </c>
+      <c r="B16" s="12">
+        <f>IF('Sources &amp; Uses'!B36=0,0,(SUMPRODUCT(MAX(B10:G10,0))/'Sources &amp; Uses'!B36))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="31" t="inlineStr">
+        <is>
           <t>Development Spread (YoC - Exit Cap)</t>
         </is>
       </c>
-      <c r="B16" s="10">
+      <c r="B17" s="10">
         <f>'NOI &amp; Cash Flow'!B11-'NOI &amp; Cash Flow'!B20</f>
         <v/>
       </c>
@@ -4164,7 +4198,7 @@
         </is>
       </c>
       <c r="B7" s="11">
-        <f>'Waterfall'!B13</f>
+        <f>'Waterfall'!B14</f>
         <v/>
       </c>
     </row>
@@ -4175,7 +4209,7 @@
         </is>
       </c>
       <c r="B8" s="11">
-        <f>'Waterfall'!B14</f>
+        <f>'Waterfall'!B15</f>
         <v/>
       </c>
     </row>
@@ -4186,7 +4220,7 @@
         </is>
       </c>
       <c r="B9" s="12">
-        <f>'Waterfall'!B15</f>
+        <f>'Waterfall'!B16</f>
         <v/>
       </c>
     </row>
@@ -4208,7 +4242,7 @@
         </is>
       </c>
       <c r="B11" s="10">
-        <f>'Waterfall'!B16</f>
+        <f>'Waterfall'!B17</f>
         <v/>
       </c>
     </row>

--- a/public/demos/re-developer/dev-pro-forma.xlsx
+++ b/public/demos/re-developer/dev-pro-forma.xlsx
@@ -685,7 +685,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>The Reserve at Royal Oak</t>
+          <t>Meridian Heights</t>
         </is>
       </c>
     </row>
@@ -699,14 +699,14 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>1200 N Main St, Royal Oak, MI 48067</t>
+          <t>4500 Meridian Parkway, Columbus, OH 43215</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Prepared by 1404 Labs — 2026-04-03</t>
+          <t>Prepared by Tangent Development — 2026-04-09</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
         </is>
       </c>
       <c r="B9" s="8" t="n">
-        <v>178000</v>
+        <v>176000</v>
       </c>
     </row>
     <row r="10">
@@ -760,7 +760,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>4.2</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="11">
@@ -771,7 +771,7 @@
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>20 months</t>
+          <t>18 months</t>
         </is>
       </c>
     </row>
@@ -993,7 +993,7 @@
         </is>
       </c>
       <c r="B34" s="13">
-        <f>'Sources &amp; Uses'!B30/178000</f>
+        <f>'Sources &amp; Uses'!B30/176000</f>
         <v/>
       </c>
     </row>
@@ -1059,7 +1059,7 @@
       </c>
       <c r="B3" s="15" t="inlineStr">
         <is>
-          <t>The Reserve at Royal Oak</t>
+          <t>Meridian Heights</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr"/>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="B4" s="15" t="inlineStr">
         <is>
-          <t>1200 N Main St, Royal Oak, MI 48067</t>
+          <t>4500 Meridian Parkway, Columbus, OH 43215</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr"/>
@@ -1116,7 +1116,7 @@
         </is>
       </c>
       <c r="B7" s="17" t="n">
-        <v>178000</v>
+        <v>176000</v>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         </is>
       </c>
       <c r="B8" s="17" t="n">
-        <v>209411.7647058823</v>
+        <v>209523.8095238095</v>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
@@ -1148,7 +1148,7 @@
         </is>
       </c>
       <c r="B9" s="18" t="n">
-        <v>4.2</v>
+        <v>5.8</v>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr"/>
@@ -1189,7 +1189,7 @@
         </is>
       </c>
       <c r="B13" s="16" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
@@ -1312,7 +1312,7 @@
         </is>
       </c>
       <c r="B23" s="20" t="n">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
@@ -1339,7 +1339,7 @@
         </is>
       </c>
       <c r="B26" s="19" t="n">
-        <v>0.03</v>
+        <v>0.035</v>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         </is>
       </c>
       <c r="B27" s="20" t="n">
-        <v>1100</v>
+        <v>1050</v>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
@@ -1371,7 +1371,7 @@
         </is>
       </c>
       <c r="B28" s="20" t="n">
-        <v>600</v>
+        <v>550</v>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
         </is>
       </c>
       <c r="B29" s="20" t="n">
-        <v>350</v>
+        <v>325</v>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
@@ -1403,7 +1403,7 @@
         </is>
       </c>
       <c r="B30" s="20" t="n">
-        <v>250</v>
+        <v>225</v>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
@@ -1419,7 +1419,7 @@
         </is>
       </c>
       <c r="B31" s="20" t="n">
-        <v>425</v>
+        <v>400</v>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
@@ -1435,7 +1435,7 @@
         </is>
       </c>
       <c r="B32" s="20" t="n">
-        <v>240</v>
+        <v>220</v>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
@@ -1451,7 +1451,7 @@
         </is>
       </c>
       <c r="B33" s="20" t="n">
-        <v>175</v>
+        <v>190</v>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         </is>
       </c>
       <c r="B34" s="20" t="n">
-        <v>200</v>
+        <v>185</v>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
@@ -1483,7 +1483,7 @@
         </is>
       </c>
       <c r="B35" s="20" t="n">
-        <v>525</v>
+        <v>490</v>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         </is>
       </c>
       <c r="B36" s="20" t="n">
-        <v>2200</v>
+        <v>1950</v>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
@@ -1515,7 +1515,7 @@
         </is>
       </c>
       <c r="B37" s="20" t="n">
-        <v>240</v>
+        <v>220</v>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         </is>
       </c>
       <c r="B38" s="20" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
@@ -1622,7 +1622,7 @@
         </is>
       </c>
       <c r="B46" s="21" t="n">
-        <v>0.0725</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="C46" s="3" t="inlineStr"/>
       <c r="D46" s="3" t="inlineStr"/>
@@ -1634,7 +1634,7 @@
         </is>
       </c>
       <c r="B47" s="16" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
@@ -1674,7 +1674,7 @@
         </is>
       </c>
       <c r="B50" s="21" t="n">
-        <v>0.055</v>
+        <v>0.0535</v>
       </c>
       <c r="C50" s="3" t="inlineStr"/>
       <c r="D50" s="3" t="inlineStr"/>
@@ -1729,7 +1729,7 @@
         </is>
       </c>
       <c r="B55" s="21" t="n">
-        <v>0.0525</v>
+        <v>0.055</v>
       </c>
       <c r="C55" s="3" t="inlineStr"/>
       <c r="D55" s="3" t="inlineStr"/>
@@ -1837,14 +1837,14 @@
         </is>
       </c>
       <c r="B4" s="18" t="n">
-        <v>5800000</v>
+        <v>4200000</v>
       </c>
       <c r="C4" s="22">
         <f>B4/200</f>
         <v/>
       </c>
       <c r="D4" s="22">
-        <f>B4/178000</f>
+        <f>B4/176000</f>
         <v/>
       </c>
       <c r="E4" s="23">
@@ -1871,14 +1871,14 @@
         </is>
       </c>
       <c r="B7" s="18" t="n">
-        <v>36647058.82352941</v>
+        <v>34571428.57142857</v>
       </c>
       <c r="C7" s="22">
         <f>B7/200</f>
         <v/>
       </c>
       <c r="D7" s="22">
-        <f>B7/178000</f>
+        <f>B7/176000</f>
         <v/>
       </c>
       <c r="E7" s="23">
@@ -1893,14 +1893,14 @@
         </is>
       </c>
       <c r="B8" s="18" t="n">
-        <v>2800000</v>
+        <v>2450000</v>
       </c>
       <c r="C8" s="22">
         <f>B8/200</f>
         <v/>
       </c>
       <c r="D8" s="22">
-        <f>B8/178000</f>
+        <f>B8/176000</f>
         <v/>
       </c>
       <c r="E8" s="23">
@@ -1923,7 +1923,7 @@
         <v/>
       </c>
       <c r="D9" s="22">
-        <f>B9/178000</f>
+        <f>B9/176000</f>
         <v/>
       </c>
       <c r="E9" s="23">
@@ -1946,7 +1946,7 @@
         <v/>
       </c>
       <c r="D10" s="26">
-        <f>B10/178000</f>
+        <f>B10/176000</f>
         <v/>
       </c>
       <c r="E10" s="23">
@@ -1973,14 +1973,14 @@
         </is>
       </c>
       <c r="B13" s="18" t="n">
-        <v>2800000</v>
+        <v>2350000</v>
       </c>
       <c r="C13" s="22">
         <f>B13/200</f>
         <v/>
       </c>
       <c r="D13" s="22">
-        <f>B13/178000</f>
+        <f>B13/176000</f>
         <v/>
       </c>
       <c r="E13" s="23">
@@ -1995,14 +1995,14 @@
         </is>
       </c>
       <c r="B14" s="18" t="n">
-        <v>1600000</v>
+        <v>1400000</v>
       </c>
       <c r="C14" s="22">
         <f>B14/200</f>
         <v/>
       </c>
       <c r="D14" s="22">
-        <f>B14/178000</f>
+        <f>B14/176000</f>
         <v/>
       </c>
       <c r="E14" s="23">
@@ -2017,14 +2017,14 @@
         </is>
       </c>
       <c r="B15" s="18" t="n">
-        <v>450000</v>
+        <v>380000</v>
       </c>
       <c r="C15" s="22">
         <f>B15/200</f>
         <v/>
       </c>
       <c r="D15" s="22">
-        <f>B15/178000</f>
+        <f>B15/176000</f>
         <v/>
       </c>
       <c r="E15" s="23">
@@ -2039,14 +2039,14 @@
         </is>
       </c>
       <c r="B16" s="18" t="n">
-        <v>380000</v>
+        <v>310000</v>
       </c>
       <c r="C16" s="22">
         <f>B16/200</f>
         <v/>
       </c>
       <c r="D16" s="22">
-        <f>B16/178000</f>
+        <f>B16/176000</f>
         <v/>
       </c>
       <c r="E16" s="23">
@@ -2061,14 +2061,14 @@
         </is>
       </c>
       <c r="B17" s="18" t="n">
-        <v>500000</v>
+        <v>450000</v>
       </c>
       <c r="C17" s="22">
         <f>B17/200</f>
         <v/>
       </c>
       <c r="D17" s="22">
-        <f>B17/178000</f>
+        <f>B17/176000</f>
         <v/>
       </c>
       <c r="E17" s="23">
@@ -2083,14 +2083,14 @@
         </is>
       </c>
       <c r="B18" s="18" t="n">
-        <v>320000</v>
+        <v>275000</v>
       </c>
       <c r="C18" s="22">
         <f>B18/200</f>
         <v/>
       </c>
       <c r="D18" s="22">
-        <f>B18/178000</f>
+        <f>B18/176000</f>
         <v/>
       </c>
       <c r="E18" s="23">
@@ -2105,14 +2105,14 @@
         </is>
       </c>
       <c r="B19" s="18" t="n">
-        <v>175000</v>
+        <v>155000</v>
       </c>
       <c r="C19" s="22">
         <f>B19/200</f>
         <v/>
       </c>
       <c r="D19" s="22">
-        <f>B19/178000</f>
+        <f>B19/176000</f>
         <v/>
       </c>
       <c r="E19" s="23">
@@ -2135,7 +2135,7 @@
         <v/>
       </c>
       <c r="D20" s="22">
-        <f>B20/178000</f>
+        <f>B20/176000</f>
         <v/>
       </c>
       <c r="E20" s="23">
@@ -2158,7 +2158,7 @@
         <v/>
       </c>
       <c r="D21" s="26">
-        <f>B21/178000</f>
+        <f>B21/176000</f>
         <v/>
       </c>
       <c r="E21" s="23">
@@ -2193,7 +2193,7 @@
         <v/>
       </c>
       <c r="D24" s="22">
-        <f>B24/178000</f>
+        <f>B24/176000</f>
         <v/>
       </c>
       <c r="E24" s="23">
@@ -2208,7 +2208,7 @@
         </is>
       </c>
       <c r="B25" s="9">
-        <f>B37*0.0725*0.5*20/12</f>
+        <f>B37*0.07*0.5*18/12</f>
         <v/>
       </c>
       <c r="C25" s="22">
@@ -2216,7 +2216,7 @@
         <v/>
       </c>
       <c r="D25" s="22">
-        <f>B25/178000</f>
+        <f>B25/176000</f>
         <v/>
       </c>
       <c r="E25" s="23">
@@ -2239,7 +2239,7 @@
         <v/>
       </c>
       <c r="D26" s="26">
-        <f>B26/178000</f>
+        <f>B26/176000</f>
         <v/>
       </c>
       <c r="E26" s="23">
@@ -2263,7 +2263,7 @@
         <v/>
       </c>
       <c r="D28" s="22">
-        <f>B28/178000</f>
+        <f>B28/176000</f>
         <v/>
       </c>
       <c r="E28" s="23">
@@ -2287,7 +2287,7 @@
         <v/>
       </c>
       <c r="D30" s="29">
-        <f>B30/178000</f>
+        <f>B30/176000</f>
         <v/>
       </c>
       <c r="E30" s="23">
@@ -2373,7 +2373,7 @@
         </is>
       </c>
       <c r="B37" s="9">
-        <f>(0.65*(B4+B10+B21+B28))/(1-0.65*(0.01+0.0725*0.5*20/12))</f>
+        <f>(0.65*(B4+B10+B21+B28))/(1-0.65*(0.01+0.07*0.5*18/12))</f>
         <v/>
       </c>
       <c r="C37" s="23">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>65% LTC, 7.25%</t>
+          <t>65% LTC, 7.00%</t>
         </is>
       </c>
     </row>
@@ -2524,13 +2524,13 @@
         </is>
       </c>
       <c r="B4" s="16" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C4" s="17" t="n">
-        <v>550</v>
+        <v>525</v>
       </c>
       <c r="D4" s="34" t="n">
-        <v>3.1</v>
+        <v>2.85</v>
       </c>
       <c r="E4" s="22">
         <f>C4*D4</f>
@@ -2551,10 +2551,10 @@
         <v>80</v>
       </c>
       <c r="C5" s="17" t="n">
-        <v>725</v>
+        <v>700</v>
       </c>
       <c r="D5" s="34" t="n">
-        <v>2.95</v>
+        <v>2.65</v>
       </c>
       <c r="E5" s="22">
         <f>C5*D5</f>
@@ -2575,10 +2575,10 @@
         <v>72</v>
       </c>
       <c r="C6" s="17" t="n">
-        <v>1050</v>
+        <v>1025</v>
       </c>
       <c r="D6" s="34" t="n">
-        <v>2.75</v>
+        <v>2.45</v>
       </c>
       <c r="E6" s="22">
         <f>C6*D6</f>
@@ -2596,13 +2596,13 @@
         </is>
       </c>
       <c r="B7" s="16" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="C7" s="17" t="n">
-        <v>1300</v>
+        <v>1275</v>
       </c>
       <c r="D7" s="34" t="n">
-        <v>2.55</v>
+        <v>2.25</v>
       </c>
       <c r="E7" s="22">
         <f>C7*D7</f>
@@ -2795,7 +2795,7 @@
         </is>
       </c>
       <c r="B16" s="18" t="n">
-        <v>300000</v>
+        <v>276000</v>
       </c>
       <c r="C16" s="9">
         <f>B16*(1+0.03)</f>
@@ -2912,27 +2912,27 @@
       </c>
       <c r="B2" s="15" t="inlineStr">
         <is>
-          <t>3.0% EGI</t>
+          <t>3.5% EGI</t>
         </is>
       </c>
       <c r="C2" s="9">
-        <f>'Revenue'!B18*0.03</f>
+        <f>'Revenue'!B18*0.035</f>
         <v/>
       </c>
       <c r="D2" s="9">
-        <f>'Revenue'!C18*0.03</f>
+        <f>'Revenue'!C18*0.035</f>
         <v/>
       </c>
       <c r="E2" s="9">
-        <f>'Revenue'!D18*0.03</f>
+        <f>'Revenue'!D18*0.035</f>
         <v/>
       </c>
       <c r="F2" s="9">
-        <f>'Revenue'!E18*0.03</f>
+        <f>'Revenue'!E18*0.035</f>
         <v/>
       </c>
       <c r="G2" s="9">
-        <f>'Revenue'!F18*0.03</f>
+        <f>'Revenue'!F18*0.035</f>
         <v/>
       </c>
     </row>
@@ -2943,10 +2943,10 @@
         </is>
       </c>
       <c r="B3" s="20" t="n">
-        <v>1100</v>
+        <v>1050</v>
       </c>
       <c r="C3" s="18" t="n">
-        <v>220000</v>
+        <v>210000</v>
       </c>
       <c r="D3" s="9">
         <f>C3*(1+0.03)</f>
@@ -2972,10 +2972,10 @@
         </is>
       </c>
       <c r="B4" s="20" t="n">
-        <v>600</v>
+        <v>550</v>
       </c>
       <c r="C4" s="18" t="n">
-        <v>120000</v>
+        <v>110000</v>
       </c>
       <c r="D4" s="9">
         <f>C4*(1+0.03)</f>
@@ -3001,10 +3001,10 @@
         </is>
       </c>
       <c r="B5" s="20" t="n">
-        <v>350</v>
+        <v>325</v>
       </c>
       <c r="C5" s="18" t="n">
-        <v>70000</v>
+        <v>65000</v>
       </c>
       <c r="D5" s="9">
         <f>C5*(1+0.03)</f>
@@ -3030,10 +3030,10 @@
         </is>
       </c>
       <c r="B6" s="20" t="n">
-        <v>250</v>
+        <v>225</v>
       </c>
       <c r="C6" s="18" t="n">
-        <v>50000</v>
+        <v>45000</v>
       </c>
       <c r="D6" s="9">
         <f>C6*(1+0.03)</f>
@@ -3059,10 +3059,10 @@
         </is>
       </c>
       <c r="B7" s="20" t="n">
-        <v>425</v>
+        <v>400</v>
       </c>
       <c r="C7" s="18" t="n">
-        <v>85000</v>
+        <v>80000</v>
       </c>
       <c r="D7" s="9">
         <f>C7*(1+0.03)</f>
@@ -3088,10 +3088,10 @@
         </is>
       </c>
       <c r="B8" s="20" t="n">
-        <v>240</v>
+        <v>220</v>
       </c>
       <c r="C8" s="18" t="n">
-        <v>48000</v>
+        <v>44000</v>
       </c>
       <c r="D8" s="9">
         <f>C8*(1+0.03)</f>
@@ -3117,10 +3117,10 @@
         </is>
       </c>
       <c r="B9" s="20" t="n">
-        <v>175</v>
+        <v>190</v>
       </c>
       <c r="C9" s="18" t="n">
-        <v>35000</v>
+        <v>38000</v>
       </c>
       <c r="D9" s="9">
         <f>C9*(1+0.03)</f>
@@ -3146,10 +3146,10 @@
         </is>
       </c>
       <c r="B10" s="20" t="n">
-        <v>200</v>
+        <v>185</v>
       </c>
       <c r="C10" s="18" t="n">
-        <v>40000</v>
+        <v>37000</v>
       </c>
       <c r="D10" s="9">
         <f>C10*(1+0.03)</f>
@@ -3175,10 +3175,10 @@
         </is>
       </c>
       <c r="B11" s="20" t="n">
-        <v>525</v>
+        <v>490</v>
       </c>
       <c r="C11" s="18" t="n">
-        <v>105000</v>
+        <v>98000</v>
       </c>
       <c r="D11" s="9">
         <f>C11*(1+0.07)</f>
@@ -3204,10 +3204,10 @@
         </is>
       </c>
       <c r="B12" s="20" t="n">
-        <v>2200</v>
+        <v>1950</v>
       </c>
       <c r="C12" s="18" t="n">
-        <v>440000</v>
+        <v>390000</v>
       </c>
       <c r="D12" s="9">
         <f>C12*(1+0.03)</f>
@@ -3233,10 +3233,10 @@
         </is>
       </c>
       <c r="B13" s="20" t="n">
-        <v>240</v>
+        <v>220</v>
       </c>
       <c r="C13" s="18" t="n">
-        <v>48000</v>
+        <v>44000</v>
       </c>
       <c r="D13" s="9">
         <f>C13*(1+0.03)</f>
@@ -3262,10 +3262,10 @@
         </is>
       </c>
       <c r="B14" s="20" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="C14" s="18" t="n">
-        <v>30000</v>
+        <v>28000</v>
       </c>
       <c r="D14" s="9">
         <f>C14*(1+0.03)</f>
@@ -3542,23 +3542,23 @@
         </is>
       </c>
       <c r="B7" s="9">
-        <f>PMT(0.055/12,30*12,'Sources &amp; Uses'!B30*0.65)*12</f>
+        <f>PMT(0.0535/12,30*12,'Sources &amp; Uses'!B30*0.65)*12</f>
         <v/>
       </c>
       <c r="C7" s="9">
-        <f>PMT(0.055/12,30*12,'Sources &amp; Uses'!B30*0.65)*12</f>
+        <f>PMT(0.0535/12,30*12,'Sources &amp; Uses'!B30*0.65)*12</f>
         <v/>
       </c>
       <c r="D7" s="9">
-        <f>PMT(0.055/12,30*12,'Sources &amp; Uses'!B30*0.65)*12</f>
+        <f>PMT(0.0535/12,30*12,'Sources &amp; Uses'!B30*0.65)*12</f>
         <v/>
       </c>
       <c r="E7" s="9">
-        <f>PMT(0.055/12,30*12,'Sources &amp; Uses'!B30*0.65)*12</f>
+        <f>PMT(0.0535/12,30*12,'Sources &amp; Uses'!B30*0.65)*12</f>
         <v/>
       </c>
       <c r="F7" s="9">
-        <f>PMT(0.055/12,30*12,'Sources &amp; Uses'!B30*0.65)*12</f>
+        <f>PMT(0.0535/12,30*12,'Sources &amp; Uses'!B30*0.65)*12</f>
         <v/>
       </c>
     </row>
@@ -3714,7 +3714,7 @@
         </is>
       </c>
       <c r="B17" s="9">
-        <f>B16/0.0525</f>
+        <f>B16/0.055</f>
         <v/>
       </c>
     </row>
@@ -3747,7 +3747,7 @@
         </is>
       </c>
       <c r="B20" s="21" t="n">
-        <v>0.0525</v>
+        <v>0.055</v>
       </c>
     </row>
   </sheetData>
@@ -3956,7 +3956,7 @@
         <v>0</v>
       </c>
       <c r="G6" s="9">
-        <f>FV(0.055/12,5*12,PMT(0.055/12,30*12,('Sources &amp; Uses'!B30*0.65)),('Sources &amp; Uses'!B30*0.65))</f>
+        <f>FV(0.0535/12,5*12,PMT(0.0535/12,30*12,('Sources &amp; Uses'!B30*0.65)),('Sources &amp; Uses'!B30*0.65))</f>
         <v/>
       </c>
       <c r="H6" s="9">

--- a/public/demos/re-developer/dev-pro-forma.xlsx
+++ b/public/demos/re-developer/dev-pro-forma.xlsx
@@ -685,7 +685,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Meridian Heights</t>
+          <t>The Reserve at Royal Oak</t>
         </is>
       </c>
     </row>
@@ -699,14 +699,14 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>4500 Meridian Parkway, Columbus, OH 43215</t>
+          <t>1200 N Main St, Royal Oak, MI 48067</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Prepared by Tangent Development — 2026-04-09</t>
+          <t>Prepared by 1404 Labs — 2026-04-03</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
         </is>
       </c>
       <c r="B9" s="8" t="n">
-        <v>176000</v>
+        <v>178000</v>
       </c>
     </row>
     <row r="10">
@@ -760,7 +760,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>5.8</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="11">
@@ -771,7 +771,7 @@
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>18 months</t>
+          <t>20 months</t>
         </is>
       </c>
     </row>
@@ -993,7 +993,7 @@
         </is>
       </c>
       <c r="B34" s="13">
-        <f>'Sources &amp; Uses'!B30/176000</f>
+        <f>'Sources &amp; Uses'!B30/178000</f>
         <v/>
       </c>
     </row>
@@ -1059,7 +1059,7 @@
       </c>
       <c r="B3" s="15" t="inlineStr">
         <is>
-          <t>Meridian Heights</t>
+          <t>The Reserve at Royal Oak</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr"/>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="B4" s="15" t="inlineStr">
         <is>
-          <t>4500 Meridian Parkway, Columbus, OH 43215</t>
+          <t>1200 N Main St, Royal Oak, MI 48067</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr"/>
@@ -1116,7 +1116,7 @@
         </is>
       </c>
       <c r="B7" s="17" t="n">
-        <v>176000</v>
+        <v>178000</v>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         </is>
       </c>
       <c r="B8" s="17" t="n">
-        <v>209523.8095238095</v>
+        <v>209411.7647058823</v>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
@@ -1148,7 +1148,7 @@
         </is>
       </c>
       <c r="B9" s="18" t="n">
-        <v>5.8</v>
+        <v>4.2</v>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr"/>
@@ -1189,7 +1189,7 @@
         </is>
       </c>
       <c r="B13" s="16" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
@@ -1312,7 +1312,7 @@
         </is>
       </c>
       <c r="B23" s="20" t="n">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
@@ -1339,7 +1339,7 @@
         </is>
       </c>
       <c r="B26" s="19" t="n">
-        <v>0.035</v>
+        <v>0.03</v>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         </is>
       </c>
       <c r="B27" s="20" t="n">
-        <v>1050</v>
+        <v>1100</v>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
@@ -1371,7 +1371,7 @@
         </is>
       </c>
       <c r="B28" s="20" t="n">
-        <v>550</v>
+        <v>600</v>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
         </is>
       </c>
       <c r="B29" s="20" t="n">
-        <v>325</v>
+        <v>350</v>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
@@ -1403,7 +1403,7 @@
         </is>
       </c>
       <c r="B30" s="20" t="n">
-        <v>225</v>
+        <v>250</v>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
@@ -1419,7 +1419,7 @@
         </is>
       </c>
       <c r="B31" s="20" t="n">
-        <v>400</v>
+        <v>425</v>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
@@ -1435,7 +1435,7 @@
         </is>
       </c>
       <c r="B32" s="20" t="n">
-        <v>220</v>
+        <v>240</v>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
@@ -1451,7 +1451,7 @@
         </is>
       </c>
       <c r="B33" s="20" t="n">
-        <v>190</v>
+        <v>175</v>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         </is>
       </c>
       <c r="B34" s="20" t="n">
-        <v>185</v>
+        <v>200</v>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
@@ -1483,7 +1483,7 @@
         </is>
       </c>
       <c r="B35" s="20" t="n">
-        <v>490</v>
+        <v>525</v>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         </is>
       </c>
       <c r="B36" s="20" t="n">
-        <v>1950</v>
+        <v>2200</v>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
@@ -1515,7 +1515,7 @@
         </is>
       </c>
       <c r="B37" s="20" t="n">
-        <v>220</v>
+        <v>240</v>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         </is>
       </c>
       <c r="B38" s="20" t="n">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
@@ -1622,7 +1622,7 @@
         </is>
       </c>
       <c r="B46" s="21" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.0725</v>
       </c>
       <c r="C46" s="3" t="inlineStr"/>
       <c r="D46" s="3" t="inlineStr"/>
@@ -1634,7 +1634,7 @@
         </is>
       </c>
       <c r="B47" s="16" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
@@ -1674,7 +1674,7 @@
         </is>
       </c>
       <c r="B50" s="21" t="n">
-        <v>0.0535</v>
+        <v>0.055</v>
       </c>
       <c r="C50" s="3" t="inlineStr"/>
       <c r="D50" s="3" t="inlineStr"/>
@@ -1729,7 +1729,7 @@
         </is>
       </c>
       <c r="B55" s="21" t="n">
-        <v>0.055</v>
+        <v>0.0525</v>
       </c>
       <c r="C55" s="3" t="inlineStr"/>
       <c r="D55" s="3" t="inlineStr"/>
@@ -1837,14 +1837,14 @@
         </is>
       </c>
       <c r="B4" s="18" t="n">
-        <v>4200000</v>
+        <v>5800000</v>
       </c>
       <c r="C4" s="22">
         <f>B4/200</f>
         <v/>
       </c>
       <c r="D4" s="22">
-        <f>B4/176000</f>
+        <f>B4/178000</f>
         <v/>
       </c>
       <c r="E4" s="23">
@@ -1871,14 +1871,14 @@
         </is>
       </c>
       <c r="B7" s="18" t="n">
-        <v>34571428.57142857</v>
+        <v>36647058.82352941</v>
       </c>
       <c r="C7" s="22">
         <f>B7/200</f>
         <v/>
       </c>
       <c r="D7" s="22">
-        <f>B7/176000</f>
+        <f>B7/178000</f>
         <v/>
       </c>
       <c r="E7" s="23">
@@ -1893,14 +1893,14 @@
         </is>
       </c>
       <c r="B8" s="18" t="n">
-        <v>2450000</v>
+        <v>2800000</v>
       </c>
       <c r="C8" s="22">
         <f>B8/200</f>
         <v/>
       </c>
       <c r="D8" s="22">
-        <f>B8/176000</f>
+        <f>B8/178000</f>
         <v/>
       </c>
       <c r="E8" s="23">
@@ -1923,7 +1923,7 @@
         <v/>
       </c>
       <c r="D9" s="22">
-        <f>B9/176000</f>
+        <f>B9/178000</f>
         <v/>
       </c>
       <c r="E9" s="23">
@@ -1946,7 +1946,7 @@
         <v/>
       </c>
       <c r="D10" s="26">
-        <f>B10/176000</f>
+        <f>B10/178000</f>
         <v/>
       </c>
       <c r="E10" s="23">
@@ -1973,14 +1973,14 @@
         </is>
       </c>
       <c r="B13" s="18" t="n">
-        <v>2350000</v>
+        <v>2800000</v>
       </c>
       <c r="C13" s="22">
         <f>B13/200</f>
         <v/>
       </c>
       <c r="D13" s="22">
-        <f>B13/176000</f>
+        <f>B13/178000</f>
         <v/>
       </c>
       <c r="E13" s="23">
@@ -1995,14 +1995,14 @@
         </is>
       </c>
       <c r="B14" s="18" t="n">
-        <v>1400000</v>
+        <v>1600000</v>
       </c>
       <c r="C14" s="22">
         <f>B14/200</f>
         <v/>
       </c>
       <c r="D14" s="22">
-        <f>B14/176000</f>
+        <f>B14/178000</f>
         <v/>
       </c>
       <c r="E14" s="23">
@@ -2017,14 +2017,14 @@
         </is>
       </c>
       <c r="B15" s="18" t="n">
-        <v>380000</v>
+        <v>450000</v>
       </c>
       <c r="C15" s="22">
         <f>B15/200</f>
         <v/>
       </c>
       <c r="D15" s="22">
-        <f>B15/176000</f>
+        <f>B15/178000</f>
         <v/>
       </c>
       <c r="E15" s="23">
@@ -2039,14 +2039,14 @@
         </is>
       </c>
       <c r="B16" s="18" t="n">
-        <v>310000</v>
+        <v>380000</v>
       </c>
       <c r="C16" s="22">
         <f>B16/200</f>
         <v/>
       </c>
       <c r="D16" s="22">
-        <f>B16/176000</f>
+        <f>B16/178000</f>
         <v/>
       </c>
       <c r="E16" s="23">
@@ -2061,14 +2061,14 @@
         </is>
       </c>
       <c r="B17" s="18" t="n">
-        <v>450000</v>
+        <v>500000</v>
       </c>
       <c r="C17" s="22">
         <f>B17/200</f>
         <v/>
       </c>
       <c r="D17" s="22">
-        <f>B17/176000</f>
+        <f>B17/178000</f>
         <v/>
       </c>
       <c r="E17" s="23">
@@ -2083,14 +2083,14 @@
         </is>
       </c>
       <c r="B18" s="18" t="n">
-        <v>275000</v>
+        <v>320000</v>
       </c>
       <c r="C18" s="22">
         <f>B18/200</f>
         <v/>
       </c>
       <c r="D18" s="22">
-        <f>B18/176000</f>
+        <f>B18/178000</f>
         <v/>
       </c>
       <c r="E18" s="23">
@@ -2105,14 +2105,14 @@
         </is>
       </c>
       <c r="B19" s="18" t="n">
-        <v>155000</v>
+        <v>175000</v>
       </c>
       <c r="C19" s="22">
         <f>B19/200</f>
         <v/>
       </c>
       <c r="D19" s="22">
-        <f>B19/176000</f>
+        <f>B19/178000</f>
         <v/>
       </c>
       <c r="E19" s="23">
@@ -2135,7 +2135,7 @@
         <v/>
       </c>
       <c r="D20" s="22">
-        <f>B20/176000</f>
+        <f>B20/178000</f>
         <v/>
       </c>
       <c r="E20" s="23">
@@ -2158,7 +2158,7 @@
         <v/>
       </c>
       <c r="D21" s="26">
-        <f>B21/176000</f>
+        <f>B21/178000</f>
         <v/>
       </c>
       <c r="E21" s="23">
@@ -2193,7 +2193,7 @@
         <v/>
       </c>
       <c r="D24" s="22">
-        <f>B24/176000</f>
+        <f>B24/178000</f>
         <v/>
       </c>
       <c r="E24" s="23">
@@ -2208,7 +2208,7 @@
         </is>
       </c>
       <c r="B25" s="9">
-        <f>B37*0.07*0.5*18/12</f>
+        <f>B37*0.0725*0.5*20/12</f>
         <v/>
       </c>
       <c r="C25" s="22">
@@ -2216,7 +2216,7 @@
         <v/>
       </c>
       <c r="D25" s="22">
-        <f>B25/176000</f>
+        <f>B25/178000</f>
         <v/>
       </c>
       <c r="E25" s="23">
@@ -2239,7 +2239,7 @@
         <v/>
       </c>
       <c r="D26" s="26">
-        <f>B26/176000</f>
+        <f>B26/178000</f>
         <v/>
       </c>
       <c r="E26" s="23">
@@ -2263,7 +2263,7 @@
         <v/>
       </c>
       <c r="D28" s="22">
-        <f>B28/176000</f>
+        <f>B28/178000</f>
         <v/>
       </c>
       <c r="E28" s="23">
@@ -2287,7 +2287,7 @@
         <v/>
       </c>
       <c r="D30" s="29">
-        <f>B30/176000</f>
+        <f>B30/178000</f>
         <v/>
       </c>
       <c r="E30" s="23">
@@ -2373,7 +2373,7 @@
         </is>
       </c>
       <c r="B37" s="9">
-        <f>(0.65*(B4+B10+B21+B28))/(1-0.65*(0.01+0.07*0.5*18/12))</f>
+        <f>(0.65*(B4+B10+B21+B28))/(1-0.65*(0.01+0.0725*0.5*20/12))</f>
         <v/>
       </c>
       <c r="C37" s="23">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>65% LTC, 7.00%</t>
+          <t>65% LTC, 7.25%</t>
         </is>
       </c>
     </row>
@@ -2524,13 +2524,13 @@
         </is>
       </c>
       <c r="B4" s="16" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C4" s="17" t="n">
-        <v>525</v>
+        <v>550</v>
       </c>
       <c r="D4" s="34" t="n">
-        <v>2.85</v>
+        <v>3.1</v>
       </c>
       <c r="E4" s="22">
         <f>C4*D4</f>
@@ -2551,10 +2551,10 @@
         <v>80</v>
       </c>
       <c r="C5" s="17" t="n">
-        <v>700</v>
+        <v>725</v>
       </c>
       <c r="D5" s="34" t="n">
-        <v>2.65</v>
+        <v>2.95</v>
       </c>
       <c r="E5" s="22">
         <f>C5*D5</f>
@@ -2575,10 +2575,10 @@
         <v>72</v>
       </c>
       <c r="C6" s="17" t="n">
-        <v>1025</v>
+        <v>1050</v>
       </c>
       <c r="D6" s="34" t="n">
-        <v>2.45</v>
+        <v>2.75</v>
       </c>
       <c r="E6" s="22">
         <f>C6*D6</f>
@@ -2596,13 +2596,13 @@
         </is>
       </c>
       <c r="B7" s="16" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C7" s="17" t="n">
-        <v>1275</v>
+        <v>1300</v>
       </c>
       <c r="D7" s="34" t="n">
-        <v>2.25</v>
+        <v>2.55</v>
       </c>
       <c r="E7" s="22">
         <f>C7*D7</f>
@@ -2795,7 +2795,7 @@
         </is>
       </c>
       <c r="B16" s="18" t="n">
-        <v>276000</v>
+        <v>300000</v>
       </c>
       <c r="C16" s="9">
         <f>B16*(1+0.03)</f>
@@ -2912,27 +2912,27 @@
       </c>
       <c r="B2" s="15" t="inlineStr">
         <is>
-          <t>3.5% EGI</t>
+          <t>3.0% EGI</t>
         </is>
       </c>
       <c r="C2" s="9">
-        <f>'Revenue'!B18*0.035</f>
+        <f>'Revenue'!B18*0.03</f>
         <v/>
       </c>
       <c r="D2" s="9">
-        <f>'Revenue'!C18*0.035</f>
+        <f>'Revenue'!C18*0.03</f>
         <v/>
       </c>
       <c r="E2" s="9">
-        <f>'Revenue'!D18*0.035</f>
+        <f>'Revenue'!D18*0.03</f>
         <v/>
       </c>
       <c r="F2" s="9">
-        <f>'Revenue'!E18*0.035</f>
+        <f>'Revenue'!E18*0.03</f>
         <v/>
       </c>
       <c r="G2" s="9">
-        <f>'Revenue'!F18*0.035</f>
+        <f>'Revenue'!F18*0.03</f>
         <v/>
       </c>
     </row>
@@ -2943,10 +2943,10 @@
         </is>
       </c>
       <c r="B3" s="20" t="n">
-        <v>1050</v>
+        <v>1100</v>
       </c>
       <c r="C3" s="18" t="n">
-        <v>210000</v>
+        <v>220000</v>
       </c>
       <c r="D3" s="9">
         <f>C3*(1+0.03)</f>
@@ -2972,10 +2972,10 @@
         </is>
       </c>
       <c r="B4" s="20" t="n">
-        <v>550</v>
+        <v>600</v>
       </c>
       <c r="C4" s="18" t="n">
-        <v>110000</v>
+        <v>120000</v>
       </c>
       <c r="D4" s="9">
         <f>C4*(1+0.03)</f>
@@ -3001,10 +3001,10 @@
         </is>
       </c>
       <c r="B5" s="20" t="n">
-        <v>325</v>
+        <v>350</v>
       </c>
       <c r="C5" s="18" t="n">
-        <v>65000</v>
+        <v>70000</v>
       </c>
       <c r="D5" s="9">
         <f>C5*(1+0.03)</f>
@@ -3030,10 +3030,10 @@
         </is>
       </c>
       <c r="B6" s="20" t="n">
-        <v>225</v>
+        <v>250</v>
       </c>
       <c r="C6" s="18" t="n">
-        <v>45000</v>
+        <v>50000</v>
       </c>
       <c r="D6" s="9">
         <f>C6*(1+0.03)</f>
@@ -3059,10 +3059,10 @@
         </is>
       </c>
       <c r="B7" s="20" t="n">
-        <v>400</v>
+        <v>425</v>
       </c>
       <c r="C7" s="18" t="n">
-        <v>80000</v>
+        <v>85000</v>
       </c>
       <c r="D7" s="9">
         <f>C7*(1+0.03)</f>
@@ -3088,10 +3088,10 @@
         </is>
       </c>
       <c r="B8" s="20" t="n">
-        <v>220</v>
+        <v>240</v>
       </c>
       <c r="C8" s="18" t="n">
-        <v>44000</v>
+        <v>48000</v>
       </c>
       <c r="D8" s="9">
         <f>C8*(1+0.03)</f>
@@ -3117,10 +3117,10 @@
         </is>
       </c>
       <c r="B9" s="20" t="n">
-        <v>190</v>
+        <v>175</v>
       </c>
       <c r="C9" s="18" t="n">
-        <v>38000</v>
+        <v>35000</v>
       </c>
       <c r="D9" s="9">
         <f>C9*(1+0.03)</f>
@@ -3146,10 +3146,10 @@
         </is>
       </c>
       <c r="B10" s="20" t="n">
-        <v>185</v>
+        <v>200</v>
       </c>
       <c r="C10" s="18" t="n">
-        <v>37000</v>
+        <v>40000</v>
       </c>
       <c r="D10" s="9">
         <f>C10*(1+0.03)</f>
@@ -3175,10 +3175,10 @@
         </is>
       </c>
       <c r="B11" s="20" t="n">
-        <v>490</v>
+        <v>525</v>
       </c>
       <c r="C11" s="18" t="n">
-        <v>98000</v>
+        <v>105000</v>
       </c>
       <c r="D11" s="9">
         <f>C11*(1+0.07)</f>
@@ -3204,10 +3204,10 @@
         </is>
       </c>
       <c r="B12" s="20" t="n">
-        <v>1950</v>
+        <v>2200</v>
       </c>
       <c r="C12" s="18" t="n">
-        <v>390000</v>
+        <v>440000</v>
       </c>
       <c r="D12" s="9">
         <f>C12*(1+0.03)</f>
@@ -3233,10 +3233,10 @@
         </is>
       </c>
       <c r="B13" s="20" t="n">
-        <v>220</v>
+        <v>240</v>
       </c>
       <c r="C13" s="18" t="n">
-        <v>44000</v>
+        <v>48000</v>
       </c>
       <c r="D13" s="9">
         <f>C13*(1+0.03)</f>
@@ -3262,10 +3262,10 @@
         </is>
       </c>
       <c r="B14" s="20" t="n">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="C14" s="18" t="n">
-        <v>28000</v>
+        <v>30000</v>
       </c>
       <c r="D14" s="9">
         <f>C14*(1+0.03)</f>
@@ -3542,23 +3542,23 @@
         </is>
       </c>
       <c r="B7" s="9">
-        <f>PMT(0.0535/12,30*12,'Sources &amp; Uses'!B30*0.65)*12</f>
+        <f>PMT(0.055/12,30*12,'Sources &amp; Uses'!B30*0.65)*12</f>
         <v/>
       </c>
       <c r="C7" s="9">
-        <f>PMT(0.0535/12,30*12,'Sources &amp; Uses'!B30*0.65)*12</f>
+        <f>PMT(0.055/12,30*12,'Sources &amp; Uses'!B30*0.65)*12</f>
         <v/>
       </c>
       <c r="D7" s="9">
-        <f>PMT(0.0535/12,30*12,'Sources &amp; Uses'!B30*0.65)*12</f>
+        <f>PMT(0.055/12,30*12,'Sources &amp; Uses'!B30*0.65)*12</f>
         <v/>
       </c>
       <c r="E7" s="9">
-        <f>PMT(0.0535/12,30*12,'Sources &amp; Uses'!B30*0.65)*12</f>
+        <f>PMT(0.055/12,30*12,'Sources &amp; Uses'!B30*0.65)*12</f>
         <v/>
       </c>
       <c r="F7" s="9">
-        <f>PMT(0.0535/12,30*12,'Sources &amp; Uses'!B30*0.65)*12</f>
+        <f>PMT(0.055/12,30*12,'Sources &amp; Uses'!B30*0.65)*12</f>
         <v/>
       </c>
     </row>
@@ -3714,7 +3714,7 @@
         </is>
       </c>
       <c r="B17" s="9">
-        <f>B16/0.055</f>
+        <f>B16/0.0525</f>
         <v/>
       </c>
     </row>
@@ -3747,7 +3747,7 @@
         </is>
       </c>
       <c r="B20" s="21" t="n">
-        <v>0.055</v>
+        <v>0.0525</v>
       </c>
     </row>
   </sheetData>
@@ -3956,7 +3956,7 @@
         <v>0</v>
       </c>
       <c r="G6" s="9">
-        <f>FV(0.0535/12,5*12,PMT(0.0535/12,30*12,('Sources &amp; Uses'!B30*0.65)),('Sources &amp; Uses'!B30*0.65))</f>
+        <f>FV(0.055/12,5*12,PMT(0.055/12,30*12,('Sources &amp; Uses'!B30*0.65)),('Sources &amp; Uses'!B30*0.65))</f>
         <v/>
       </c>
       <c r="H6" s="9">
